--- a/tasklist/動くAI.xlsx
+++ b/tasklist/動くAI.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
   <si>
     <t>ID</t>
   </si>
@@ -568,9 +568,6 @@
   </si>
   <si>
     <t>s</t>
-  </si>
-  <si>
-    <t>★★☆☆☆</t>
   </si>
 </sst>
 </file>
@@ -590,12 +587,10 @@
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <sz val="10.000000"/>
-      <color indexed="64"/>
       <name val="Courier New"/>
     </font>
     <font>
@@ -629,15 +624,12 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -652,10 +644,6 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1172,7 +1160,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="42.75">
+    <row r="2" ht="28.5">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1226,7 +1214,7 @@
       <c r="G3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1269,7 +1257,7 @@
       <c r="D5" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5" s="3">
         <v>10000000</v>
       </c>
       <c r="F5" s="1" t="s">
@@ -1278,7 +1266,7 @@
       <c r="G5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="J5" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1298,14 +1286,15 @@
       <c r="E6" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" ht="42.75">
+    <row r="7" ht="28.5">
       <c r="A7" s="1" t="s">
         <v>40</v>
       </c>
@@ -1367,85 +1356,85 @@
       </c>
     </row>
     <row r="9" ht="85.5">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="5"/>
+      <c r="E9" s="4"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>59</v>
       </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" ht="99.75">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="5"/>
+      <c r="E10" s="4"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>59</v>
       </c>
       <c r="J10" s="1"/>
     </row>
     <row r="11" ht="99.75">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="5"/>
+      <c r="E11" s="4"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>66</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="114">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="E12" s="5"/>
+      <c r="E12" s="4"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>59</v>
       </c>
       <c r="J12" s="1"/>
@@ -1463,7 +1452,7 @@
       <c r="D13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="5">
         <v>0.0001</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1472,7 +1461,7 @@
       <c r="G13" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1489,13 +1478,13 @@
       <c r="D14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="7">
+      <c r="E14" s="6">
         <v>0.75</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="1" t="s">
         <v>81</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -1503,491 +1492,491 @@
       </c>
     </row>
     <row r="15" ht="57">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="4" t="s">
         <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="16" ht="57">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="4" t="s">
         <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" ht="42.75">
-      <c r="A17" s="8" t="s">
+      <c r="A17" s="4" t="s">
         <v>90</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="18" ht="57">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="4" t="s">
         <v>92</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="19" ht="71.25">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="4" t="s">
         <v>94</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="20" ht="42.75">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="4" t="s">
         <v>96</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="21" ht="57">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="4" t="s">
         <v>98</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="22" ht="57">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="4" t="s">
         <v>100</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="23" ht="57">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="4" t="s">
         <v>102</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" ht="57">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="4" t="s">
         <v>104</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="4" t="s">
         <v>86</v>
       </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="54">
-      <c r="A25" s="9" t="s">
+      <c r="A25" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C25" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="G25" s="9" t="s">
         <v>109</v>
       </c>
       <c r="I25" s="1"/>
-      <c r="J25" s="3" t="s">
+      <c r="J25" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="54">
-      <c r="A26" s="9" t="s">
+      <c r="A26" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="11" t="s">
+      <c r="C26" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="G26" s="11" t="s">
+      <c r="G26" s="9" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="67.5">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="11" t="s">
+      <c r="C27" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="G27" s="11" t="s">
+      <c r="G27" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="54">
-      <c r="A28" s="12" t="s">
+      <c r="A28" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="11" t="s">
+      <c r="C28" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G28" s="11" t="s">
+      <c r="G28" s="9" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="29" ht="28.5">
-      <c r="A29" s="13" t="s">
+      <c r="A29" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="14">
+      <c r="E29" s="12">
         <v>5.02e+19</v>
       </c>
-      <c r="F29" s="13" t="s">
+      <c r="F29" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="G29" s="13" t="s">
+      <c r="G29" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
-      <c r="J29" s="13"/>
+      <c r="H29" s="11"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
     </row>
     <row r="30" ht="42.75">
-      <c r="A30" s="13" t="s">
+      <c r="A30" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="13">
+      <c r="E30" s="11">
         <v>5000</v>
       </c>
-      <c r="F30" s="13" t="s">
+      <c r="F30" s="11" t="s">
         <v>129</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G30" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
-      <c r="J30" s="13"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
     </row>
     <row r="31" ht="28.5">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="11" t="s">
         <v>131</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" s="11" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" s="11" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="13" t="s">
+      <c r="D31" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="13">
+      <c r="E31" s="11">
         <v>165</v>
       </c>
-      <c r="F31" s="13" t="s">
+      <c r="F31" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="G31" s="13" t="s">
+      <c r="G31" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
-      <c r="J31" s="13"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="13" t="s">
+      <c r="A32" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="13" t="s">
+      <c r="B32" s="11" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="13" t="s">
+      <c r="C32" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="E32" s="13">
+      <c r="E32" s="11">
         <v>45</v>
       </c>
-      <c r="F32" s="13" t="s">
+      <c r="F32" s="11" t="s">
         <v>141</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="G32" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
-      <c r="J32" s="13"/>
+      <c r="H32" s="11"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="13" t="s">
+      <c r="A33" s="11" t="s">
         <v>143</v>
       </c>
-      <c r="B33" s="13" t="s">
+      <c r="B33" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="13" t="s">
+      <c r="C33" s="11" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="13">
+      <c r="E33" s="11">
         <v>500</v>
       </c>
-      <c r="F33" s="13" t="s">
+      <c r="F33" s="11" t="s">
         <v>147</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="G33" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
-      <c r="J33" s="13"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
     </row>
     <row r="34" ht="28.5">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B34" s="13" t="s">
+      <c r="B34" s="11" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="13" t="s">
+      <c r="D34" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="13">
+      <c r="E34" s="11">
         <v>500</v>
       </c>
-      <c r="F34" s="13" t="s">
+      <c r="F34" s="11" t="s">
         <v>153</v>
       </c>
-      <c r="G34" s="13" t="s">
+      <c r="G34" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="H34" s="13"/>
-      <c r="I34" s="13"/>
-      <c r="J34" s="13"/>
+      <c r="H34" s="11"/>
+      <c r="I34" s="11"/>
+      <c r="J34" s="11"/>
     </row>
     <row r="35" ht="28.5">
-      <c r="A35" s="13" t="s">
+      <c r="A35" s="11" t="s">
         <v>155</v>
       </c>
-      <c r="B35" s="13" t="s">
+      <c r="B35" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="13" t="s">
+      <c r="C35" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="13">
         <v>1.5</v>
       </c>
-      <c r="F35" s="13" t="s">
+      <c r="F35" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="G35" s="13" t="s">
+      <c r="G35" s="11" t="s">
         <v>160</v>
       </c>
-      <c r="H35" s="13"/>
-      <c r="I35" s="13"/>
-      <c r="J35" s="13"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="13" t="s">
+      <c r="A36" s="11" t="s">
         <v>161</v>
       </c>
-      <c r="B36" s="13" t="s">
+      <c r="B36" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="C36" s="13" t="s">
+      <c r="C36" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="13">
         <v>2.5</v>
       </c>
-      <c r="F36" s="13" t="s">
+      <c r="F36" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="G36" s="13" t="s">
+      <c r="G36" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="H36" s="13"/>
-      <c r="I36" s="13"/>
-      <c r="J36" s="13"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
     </row>
     <row r="37" ht="28.5">
-      <c r="A37" s="13" t="s">
+      <c r="A37" s="11" t="s">
         <v>167</v>
       </c>
-      <c r="B37" s="13" t="s">
+      <c r="B37" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="C37" s="13" t="s">
+      <c r="C37" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="E37" s="13">
+      <c r="E37" s="11">
         <v>500</v>
       </c>
-      <c r="F37" s="13" t="s">
+      <c r="F37" s="11" t="s">
         <v>171</v>
       </c>
-      <c r="G37" s="13" t="s">
+      <c r="G37" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="H37" s="13"/>
-      <c r="I37" s="13"/>
-      <c r="J37" s="13"/>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="11"/>
     </row>
     <row r="38" ht="28.5">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="C38" s="13" t="s">
+      <c r="C38" s="11" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="13">
+      <c r="E38" s="11">
         <v>100</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="G38" s="13" t="s">
+      <c r="G38" s="11" t="s">
         <v>178</v>
       </c>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
+      <c r="H38" s="11"/>
+      <c r="I38" s="11"/>
+      <c r="J38" s="11"/>
     </row>
     <row r="39" ht="28.5">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="11" t="s">
         <v>179</v>
       </c>
-      <c r="B39" s="13" t="s">
+      <c r="B39" s="11" t="s">
         <v>180</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="C39" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="D39" s="13" t="s">
+      <c r="D39" s="11" t="s">
         <v>182</v>
       </c>
-      <c r="E39" s="16">
+      <c r="E39" s="14">
         <v>67000000</v>
       </c>
-      <c r="F39" s="13" t="s">
+      <c r="F39" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="G39" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="H39" s="13"/>
-      <c r="I39" s="13"/>
-      <c r="J39" s="13"/>
+      <c r="G39" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1"/>

--- a/tasklist/動くAI.xlsx
+++ b/tasklist/動くAI.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t>ID</t>
   </si>
@@ -192,10 +192,7 @@
     <t>温度依存摩擦モデル（アイスレオロジー）の導入</t>
   </si>
   <si>
-    <t>氷のクリープ/レオロジー特性をMaximaで定式化し、把持力の温度・時間依存性をPythonで評価する</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxima + Python</t>
+    <t>氷のクリープ/レオロジー特性を定式化し、把持力の温度・時間依存性を評価する</t>
   </si>
   <si>
     <t>PAI-18-EXT2</t>
@@ -204,7 +201,10 @@
     <t>把持面への粘着材・形状記憶合金の適用評価</t>
   </si>
   <si>
-    <t>粘着パッド・SMAグリッパーの把持力向上効果を理論計算（Maxima）と実験曲線フィッティング（Python）で比較</t>
+    <t>粘着パッド・SMAグリッパーの把持力向上効果を理論計算と実験曲線フィッティングで比較</t>
+  </si>
+  <si>
+    <t>+Maxima</t>
   </si>
   <si>
     <t>PAI-18-EXT3</t>
@@ -213,10 +213,7 @@
     <t>放射線照射試験データに基づく把持力劣化曲線</t>
   </si>
   <si>
-    <t>累積放射線量に対する材料劣化モデルをMaximaで導出し、寿命推定をPythonで実施（日本語フォント対応グラフ）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Maxima + Python (Font切り替え付き)</t>
+    <t>累積放射線量に対する材料劣化モデルをMaximaで導出し、寿命推定</t>
   </si>
   <si>
     <t>PAI-18-EXT4</t>
@@ -225,7 +222,7 @@
     <t>マニピュレータ全体の動力学解析との連成</t>
   </si>
   <si>
-    <t>把持部に働く反力をマニピュレータ動力学モデルに組み込み、制御応答をPythonでシミュレーション（Maximaでリンク方程式導出）</t>
+    <t>把持部に働く反力をマニピュレータ動力学モデルに組み込み、制御応答をシミュレーション</t>
   </si>
   <si>
     <t>PAI-19</t>
@@ -355,6 +352,12 @@
   </si>
   <si>
     <t>太陽光が硫酸雲で散乱されても発電できる多方向受光・蓄電システム。</t>
+  </si>
+  <si>
+    <t>26.05.05</t>
+  </si>
+  <si>
+    <t>有道宝庫+DS</t>
   </si>
   <si>
     <t>PA-33</t>
@@ -579,7 +582,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11.000000"/>
       <name val="Calibri"/>
@@ -592,6 +595,10 @@
     <font>
       <sz val="10.000000"/>
       <name val="Courier New"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
+      <name val="Liberation Sans"/>
     </font>
     <font>
       <sz val="11.000000"/>
@@ -624,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -636,6 +643,14 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
@@ -655,6 +670,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="4" fillId="0" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="2" borderId="0" numFmtId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1134,7 +1152,9 @@
     <col customWidth="1" min="3" max="3" style="1" width="17.28125"/>
     <col customWidth="1" min="4" max="4" style="1" width="18.7109375"/>
     <col bestFit="1" customWidth="1" min="5" max="5" style="1" width="9"/>
-    <col min="6" max="16384" style="1" width="10.28125"/>
+    <col min="6" max="10" style="1" width="10.28125"/>
+    <col customWidth="1" min="11" max="11" style="1" width="17.00390625"/>
+    <col min="12" max="16384" style="1" width="10.28125"/>
   </cols>
   <sheetData>
     <row r="1" ht="28.5">
@@ -1355,7 +1375,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" ht="85.5">
+    <row r="9" ht="71.25">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1371,33 +1391,31 @@
       <c r="E9" s="4"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="4" t="s">
-        <v>59</v>
-      </c>
+      <c r="H9" s="5"/>
       <c r="J9" s="1"/>
     </row>
-    <row r="10" ht="99.75">
+    <row r="10" ht="85.5">
       <c r="A10" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>61</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>62</v>
       </c>
       <c r="E10" s="4"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="4" t="s">
-        <v>59</v>
+      <c r="H10" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="J10" s="1"/>
     </row>
-    <row r="11" ht="99.75">
+    <row r="11" ht="57">
       <c r="A11" s="4" t="s">
         <v>48</v>
       </c>
@@ -1413,53 +1431,53 @@
       <c r="E11" s="4"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="4" t="s">
-        <v>66</v>
+      <c r="H11" s="5" t="s">
+        <v>62</v>
       </c>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" ht="114">
+    <row r="12" ht="85.5">
       <c r="A12" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="D12" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="4" t="s">
-        <v>59</v>
+      <c r="H12" s="6" t="s">
+        <v>62</v>
       </c>
       <c r="J12" s="1"/>
     </row>
     <row r="13" ht="28.5">
       <c r="A13" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="C13" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="D13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="7">
+        <v>0.0001</v>
+      </c>
+      <c r="F13" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="E13" s="5">
-        <v>0.0001</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="G13" s="1" t="s">
         <v>74</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>15</v>
@@ -1467,183 +1485,183 @@
     </row>
     <row r="14" ht="28.5">
       <c r="A14" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="C14" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="D14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="8">
+        <v>0.75</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="E14" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="J14" s="1" t="s">
         <v>81</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="15" ht="57">
       <c r="A15" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="H15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="I15" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="16" ht="57">
       <c r="A16" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="H16" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="I16" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" ht="42.75">
       <c r="A17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>91</v>
-      </c>
       <c r="H17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="18" ht="57">
       <c r="A18" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>93</v>
-      </c>
       <c r="H18" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19" ht="71.25">
       <c r="A19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>95</v>
-      </c>
       <c r="H19" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="20" ht="42.75">
       <c r="A20" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>97</v>
-      </c>
       <c r="H20" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="21" ht="57">
       <c r="A21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="H21" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" ht="57">
       <c r="A22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>101</v>
-      </c>
       <c r="H22" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="57">
       <c r="A23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="H23" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>85</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="24" ht="57">
       <c r="A24" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="H24" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="54">
+      <c r="A25" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="54">
-      <c r="A25" s="7" t="s">
+      <c r="B25" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B25" s="8" t="s">
+      <c r="C25" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="G25" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>109</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
@@ -1651,332 +1669,338 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="54">
-      <c r="A26" s="7" t="s">
+      <c r="A26" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="C26" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="G26" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G26" s="9" t="s">
-        <v>80</v>
+      <c r="K26" s="12" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="67.5">
-      <c r="A27" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="B27" s="8" t="s">
+      <c r="A27" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="C27" s="9" t="s">
+      <c r="B27" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="G27" s="9" t="s">
-        <v>75</v>
+      <c r="C27" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="54">
-      <c r="A28" s="10" t="s">
-        <v>116</v>
-      </c>
-      <c r="B28" s="8" t="s">
+      <c r="A28" s="13" t="s">
         <v>117</v>
       </c>
-      <c r="C28" s="9" t="s">
+      <c r="B28" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="G28" s="9" t="s">
-        <v>75</v>
+      <c r="C28" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="28.5">
-      <c r="A29" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B29" s="11" t="s">
+      <c r="A29" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="C29" s="11" t="s">
+      <c r="B29" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="C29" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="E29" s="12">
+      <c r="D29" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E29" s="15">
         <v>5.02e+19</v>
       </c>
-      <c r="F29" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="G29" s="11" t="s">
+      <c r="F29" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="H29" s="11"/>
-      <c r="I29" s="11"/>
-      <c r="J29" s="11"/>
+      <c r="G29" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
     </row>
     <row r="30" ht="42.75">
-      <c r="A30" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B30" s="11" t="s">
+      <c r="A30" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="C30" s="11" t="s">
+      <c r="B30" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="C30" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="E30" s="11">
+      <c r="D30" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E30" s="14">
         <v>5000</v>
       </c>
-      <c r="F30" s="11" t="s">
-        <v>129</v>
-      </c>
-      <c r="G30" s="11" t="s">
+      <c r="F30" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
+      <c r="G30" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
     </row>
     <row r="31" ht="28.5">
-      <c r="A31" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="B31" s="11" t="s">
+      <c r="A31" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="C31" s="11" t="s">
+      <c r="B31" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="C31" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="E31" s="11">
+      <c r="D31" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E31" s="14">
         <v>165</v>
       </c>
-      <c r="F31" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="G31" s="11" t="s">
+      <c r="F31" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="H31" s="11"/>
-      <c r="I31" s="11"/>
-      <c r="J31" s="11"/>
+      <c r="G31" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="B32" s="11" t="s">
+      <c r="A32" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="B32" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="C32" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="E32" s="11">
+      <c r="D32" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="14">
         <v>45</v>
       </c>
-      <c r="F32" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="G32" s="11" t="s">
+      <c r="F32" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
+      <c r="G32" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B33" s="11" t="s">
+      <c r="A33" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="C33" s="11" t="s">
+      <c r="B33" s="14" t="s">
         <v>145</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="C33" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="E33" s="11">
+      <c r="D33" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E33" s="14">
         <v>500</v>
       </c>
-      <c r="F33" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="G33" s="11" t="s">
+      <c r="F33" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="H33" s="11"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
+      <c r="G33" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
     </row>
     <row r="34" ht="28.5">
-      <c r="A34" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="B34" s="11" t="s">
+      <c r="A34" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="C34" s="11" t="s">
+      <c r="B34" s="14" t="s">
         <v>151</v>
       </c>
-      <c r="D34" s="11" t="s">
+      <c r="C34" s="14" t="s">
         <v>152</v>
       </c>
-      <c r="E34" s="11">
+      <c r="D34" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E34" s="14">
         <v>500</v>
       </c>
-      <c r="F34" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="G34" s="11" t="s">
+      <c r="F34" s="14" t="s">
         <v>154</v>
       </c>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
+      <c r="G34" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
     </row>
     <row r="35" ht="28.5">
-      <c r="A35" s="11" t="s">
-        <v>155</v>
-      </c>
-      <c r="B35" s="11" t="s">
+      <c r="A35" s="14" t="s">
         <v>156</v>
       </c>
-      <c r="C35" s="11" t="s">
+      <c r="B35" s="14" t="s">
         <v>157</v>
       </c>
-      <c r="D35" s="11" t="s">
+      <c r="C35" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="E35" s="13">
+      <c r="D35" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E35" s="16">
         <v>1.5</v>
       </c>
-      <c r="F35" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="G35" s="11" t="s">
+      <c r="F35" s="14" t="s">
         <v>160</v>
       </c>
-      <c r="H35" s="11"/>
-      <c r="I35" s="11"/>
-      <c r="J35" s="11"/>
+      <c r="G35" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="11" t="s">
-        <v>161</v>
-      </c>
-      <c r="B36" s="11" t="s">
+      <c r="A36" s="14" t="s">
         <v>162</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="B36" s="14" t="s">
         <v>163</v>
       </c>
-      <c r="D36" s="11" t="s">
+      <c r="C36" s="14" t="s">
         <v>164</v>
       </c>
-      <c r="E36" s="13">
+      <c r="D36" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E36" s="16">
         <v>2.5</v>
       </c>
-      <c r="F36" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="G36" s="11" t="s">
+      <c r="F36" s="14" t="s">
         <v>166</v>
       </c>
-      <c r="H36" s="11"/>
-      <c r="I36" s="11"/>
-      <c r="J36" s="11"/>
+      <c r="G36" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
     </row>
     <row r="37" ht="28.5">
-      <c r="A37" s="11" t="s">
-        <v>167</v>
-      </c>
-      <c r="B37" s="11" t="s">
+      <c r="A37" s="14" t="s">
         <v>168</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="B37" s="14" t="s">
         <v>169</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="C37" s="14" t="s">
         <v>170</v>
       </c>
-      <c r="E37" s="11">
+      <c r="D37" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="E37" s="14">
         <v>500</v>
       </c>
-      <c r="F37" s="11" t="s">
-        <v>171</v>
-      </c>
-      <c r="G37" s="11" t="s">
+      <c r="F37" s="14" t="s">
         <v>172</v>
       </c>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
+      <c r="G37" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
     </row>
     <row r="38" ht="28.5">
-      <c r="A38" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B38" s="11" t="s">
+      <c r="A38" s="14" t="s">
         <v>174</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="B38" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="D38" s="11" t="s">
+      <c r="C38" s="14" t="s">
         <v>176</v>
       </c>
-      <c r="E38" s="11">
+      <c r="D38" s="14" t="s">
+        <v>177</v>
+      </c>
+      <c r="E38" s="14">
         <v>100</v>
       </c>
-      <c r="F38" s="11" t="s">
-        <v>177</v>
-      </c>
-      <c r="G38" s="11" t="s">
+      <c r="F38" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="H38" s="11"/>
-      <c r="I38" s="11"/>
-      <c r="J38" s="11"/>
+      <c r="G38" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
     </row>
     <row r="39" ht="28.5">
-      <c r="A39" s="11" t="s">
-        <v>179</v>
-      </c>
-      <c r="B39" s="11" t="s">
+      <c r="A39" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="B39" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="C39" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="E39" s="14">
+      <c r="D39" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="E39" s="17">
         <v>67000000</v>
       </c>
-      <c r="F39" s="11" t="s">
-        <v>183</v>
-      </c>
-      <c r="G39" s="11" t="s">
+      <c r="F39" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="G39" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="H39" s="11"/>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1"/>

--- a/tasklist/動くAI.xlsx
+++ b/tasklist/動くAI.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>ID</t>
   </si>
@@ -273,16 +273,23 @@
     <t>Maxima</t>
   </si>
   <si>
+    <t xml:space="preserve">26.05.04
+05.23retry</t>
+  </si>
+  <si>
+    <t>POWERFUL_LLM参上</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAI-22 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gravitational Wave Coupling Efficiency</t>
+  </si>
+  <si>
+    <t>Python</t>
+  </si>
+  <si>
     <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PAI-22 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gravitational Wave Coupling Efficiency</t>
-  </si>
-  <si>
-    <t>Python</t>
   </si>
   <si>
     <t xml:space="preserve">PAI-23 </t>
@@ -650,14 +657,13 @@
       <alignment vertical="top" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="165" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
@@ -1452,7 +1458,7 @@
       <c r="E12" s="4"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>62</v>
       </c>
       <c r="J12" s="1"/>
@@ -1470,7 +1476,7 @@
       <c r="D13" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>0.0001</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -1496,7 +1502,7 @@
       <c r="D14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>0.75</v>
       </c>
       <c r="G14" s="1" t="s">
@@ -1519,149 +1525,152 @@
       <c r="H15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="8" t="s">
         <v>85</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="16" ht="57">
       <c r="A16" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" ht="42.75">
       <c r="A17" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>84</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" ht="57">
       <c r="A18" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" ht="71.25">
       <c r="A19" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>84</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" ht="42.75">
       <c r="A20" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" ht="57">
       <c r="A21" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>84</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" ht="57">
       <c r="A22" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" ht="57">
       <c r="A23" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>84</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" ht="57">
       <c r="A24" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="54">
       <c r="A25" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G25" s="11" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
@@ -1670,33 +1679,33 @@
     </row>
     <row r="26" s="1" customFormat="1" ht="54">
       <c r="A26" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="G26" s="11" t="s">
         <v>79</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K26" s="12" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="67.5">
       <c r="A27" s="13" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G27" s="11" t="s">
         <v>74</v>
@@ -1704,13 +1713,13 @@
     </row>
     <row r="28" s="1" customFormat="1" ht="54">
       <c r="A28" s="13" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="G28" s="11" t="s">
         <v>74</v>
@@ -1718,25 +1727,25 @@
     </row>
     <row r="29" ht="28.5">
       <c r="A29" s="14" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E29" s="15">
         <v>5.02e+19</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G29" s="14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H29" s="14"/>
       <c r="I29" s="14"/>
@@ -1744,25 +1753,25 @@
     </row>
     <row r="30" ht="42.75">
       <c r="A30" s="14" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B30" s="14" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E30" s="14">
         <v>5000</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G30" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="H30" s="14"/>
       <c r="I30" s="14"/>
@@ -1770,25 +1779,25 @@
     </row>
     <row r="31" ht="28.5">
       <c r="A31" s="14" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B31" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E31" s="14">
         <v>165</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G31" s="14" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="H31" s="14"/>
       <c r="I31" s="14"/>
@@ -1796,25 +1805,25 @@
     </row>
     <row r="32" ht="28.5">
       <c r="A32" s="14" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E32" s="14">
         <v>45</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G32" s="14" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H32" s="14"/>
       <c r="I32" s="14"/>
@@ -1822,25 +1831,25 @@
     </row>
     <row r="33" ht="28.5">
       <c r="A33" s="14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B33" s="14" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E33" s="14">
         <v>500</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G33" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H33" s="14"/>
       <c r="I33" s="14"/>
@@ -1848,25 +1857,25 @@
     </row>
     <row r="34" ht="28.5">
       <c r="A34" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B34" s="14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E34" s="14">
         <v>500</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G34" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H34" s="14"/>
       <c r="I34" s="14"/>
@@ -1874,25 +1883,25 @@
     </row>
     <row r="35" ht="28.5">
       <c r="A35" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B35" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E35" s="16">
         <v>1.5</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G35" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H35" s="14"/>
       <c r="I35" s="14"/>
@@ -1900,25 +1909,25 @@
     </row>
     <row r="36" ht="14.25">
       <c r="A36" s="14" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B36" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E36" s="16">
         <v>2.5</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G36" s="14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H36" s="14"/>
       <c r="I36" s="14"/>
@@ -1926,25 +1935,25 @@
     </row>
     <row r="37" ht="28.5">
       <c r="A37" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B37" s="14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E37" s="14">
         <v>500</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="G37" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
@@ -1952,25 +1961,25 @@
     </row>
     <row r="38" ht="28.5">
       <c r="A38" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B38" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E38" s="14">
         <v>100</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G38" s="14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H38" s="14"/>
       <c r="I38" s="14"/>
@@ -1978,22 +1987,22 @@
     </row>
     <row r="39" ht="28.5">
       <c r="A39" s="14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B39" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E39" s="17">
         <v>67000000</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="G39" s="14" t="s">
         <v>39</v>

--- a/tasklist/動くAI.xlsx
+++ b/tasklist/動くAI.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>ID</t>
   </si>
@@ -100,6 +100,9 @@
   </si>
   <si>
     <t>★★★★☆</t>
+  </si>
+  <si>
+    <t>POWERFUL_LLM</t>
   </si>
   <si>
     <t>PAI-11</t>
@@ -296,6 +299,9 @@
   </si>
   <si>
     <t xml:space="preserve">Exotic Matter Stability Verification</t>
+  </si>
+  <si>
+    <t>26.05.17</t>
   </si>
   <si>
     <t xml:space="preserve">PAI-24 </t>
@@ -638,12 +644,15 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="11" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -665,6 +674,7 @@
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1266,31 +1276,37 @@
       <c r="G4" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="H4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1">
+        <v>26.051500000000001</v>
+      </c>
       <c r="J4" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="5" ht="28.5">
       <c r="A5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="E5" s="3">
+        <v>32</v>
+      </c>
+      <c r="E5" s="4">
         <v>10000000</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>15</v>
@@ -1298,23 +1314,23 @@
     </row>
     <row r="6" ht="28.5">
       <c r="A6" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>15</v>
@@ -1322,31 +1338,31 @@
     </row>
     <row r="7" ht="28.5">
       <c r="A7" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2">
         <v>7440000000</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>15</v>
@@ -1354,136 +1370,136 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1">
         <v>1000</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" ht="71.25">
-      <c r="A9" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="A9" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E9" s="4"/>
+      <c r="D9" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E9" s="5"/>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="5"/>
+      <c r="H9" s="6"/>
       <c r="J9" s="1"/>
     </row>
     <row r="10" ht="85.5">
-      <c r="A10" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="4" t="s">
+      <c r="A10" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="E10" s="4"/>
+      <c r="D10" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="5"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="5" t="s">
-        <v>62</v>
+      <c r="H10" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="J10" s="1"/>
     </row>
     <row r="11" ht="57">
-      <c r="A11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="A11" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="4"/>
+      <c r="D11" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="5"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="5" t="s">
-        <v>62</v>
+      <c r="H11" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="85.5">
-      <c r="A12" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="4" t="s">
+      <c r="A12" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E12" s="4"/>
+      <c r="D12" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="5"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
-      <c r="H12" s="5" t="s">
-        <v>62</v>
+      <c r="H12" s="6" t="s">
+        <v>63</v>
       </c>
       <c r="J12" s="1"/>
     </row>
     <row r="13" ht="28.5">
       <c r="A13" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="E13" s="6">
+        <v>73</v>
+      </c>
+      <c r="E13" s="7">
         <v>0.0001</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>15</v>
@@ -1491,186 +1507,186 @@
     </row>
     <row r="14" ht="28.5">
       <c r="A14" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" s="7">
+        <v>79</v>
+      </c>
+      <c r="E14" s="8">
         <v>0.75</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" ht="57">
-      <c r="A15" s="4" t="s">
-        <v>82</v>
+      <c r="A15" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="H15" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="J15" s="8" t="s">
+      <c r="I15" s="1" t="s">
         <v>86</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="16" ht="57">
-      <c r="A16" s="4" t="s">
-        <v>87</v>
+      <c r="A16" s="5" t="s">
+        <v>88</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="H16" s="5" t="s">
         <v>90</v>
       </c>
+      <c r="I16" s="5" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="17" ht="42.75">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="I17" s="9" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="18" ht="57">
+      <c r="A18" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I17" s="4" t="s">
+    </row>
+    <row r="19" ht="71.25">
+      <c r="A19" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I19" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" ht="42.75">
+      <c r="A20" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="18" ht="57">
-      <c r="A18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I18" s="4" t="s">
+      <c r="I20" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" ht="57">
+      <c r="A21" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="22" ht="57">
+      <c r="A22" s="5" t="s">
+        <v>103</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="19" ht="71.25">
-      <c r="A19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I19" s="4" t="s">
+      <c r="I22" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" ht="57">
+      <c r="A23" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" ht="57">
+      <c r="A24" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="20" ht="42.75">
-      <c r="A20" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="21" ht="57">
-      <c r="A21" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" ht="57">
-      <c r="A22" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" ht="57">
-      <c r="A23" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" ht="57">
-      <c r="A24" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>90</v>
+      <c r="I24" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="J24" s="1"/>
     </row>
     <row r="25" s="1" customFormat="1" ht="54">
-      <c r="A25" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="C25" s="11" t="s">
+      <c r="A25" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="11" t="s">
+      <c r="B25" s="11" t="s">
         <v>110</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="I25" s="1"/>
       <c r="J25" s="1" t="s">
@@ -1678,338 +1694,338 @@
       </c>
     </row>
     <row r="26" s="1" customFormat="1" ht="54">
-      <c r="A26" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>112</v>
-      </c>
-      <c r="C26" s="11" t="s">
+      <c r="A26" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>79</v>
+      <c r="B26" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="G26" s="12" t="s">
+        <v>80</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="K26" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
+      </c>
+      <c r="K26" s="13" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="67.5">
-      <c r="A27" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="C27" s="11" t="s">
+      <c r="A27" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="G27" s="11" t="s">
-        <v>74</v>
+      <c r="B27" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" ht="54">
-      <c r="A28" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="C28" s="11" t="s">
+      <c r="A28" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>74</v>
+      <c r="B28" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="G28" s="12" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="29" ht="28.5">
-      <c r="A29" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C29" s="14" t="s">
+      <c r="A29" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="B29" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E29" s="15">
+      <c r="C29" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D29" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E29" s="16">
         <v>5.02e+19</v>
       </c>
-      <c r="F29" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="G29" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
+      <c r="F29" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
     </row>
     <row r="30" ht="42.75">
-      <c r="A30" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="C30" s="14" t="s">
+      <c r="A30" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="D30" s="14" t="s">
+      <c r="B30" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E30" s="14">
+      <c r="C30" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="15">
         <v>5000</v>
       </c>
-      <c r="F30" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
+      <c r="F30" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
     </row>
     <row r="31" ht="28.5">
-      <c r="A31" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="C31" s="14" t="s">
+      <c r="A31" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="D31" s="14" t="s">
+      <c r="B31" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="E31" s="14">
+      <c r="C31" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E31" s="15">
         <v>165</v>
       </c>
-      <c r="F31" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="G31" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
+      <c r="F31" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
     </row>
     <row r="32" ht="28.5">
-      <c r="A32" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="C32" s="14" t="s">
+      <c r="A32" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="B32" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="E32" s="14">
+      <c r="C32" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" s="15">
         <v>45</v>
       </c>
-      <c r="F32" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="G32" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
+      <c r="F32" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
     </row>
     <row r="33" ht="28.5">
-      <c r="A33" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="C33" s="14" t="s">
+      <c r="A33" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="14" t="s">
+      <c r="B33" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E33" s="14">
+      <c r="C33" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="E33" s="15">
         <v>500</v>
       </c>
-      <c r="F33" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="G33" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
+      <c r="F33" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
     </row>
     <row r="34" ht="28.5">
-      <c r="A34" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="C34" s="14" t="s">
+      <c r="A34" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="D34" s="14" t="s">
+      <c r="B34" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="E34" s="14">
+      <c r="C34" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="E34" s="15">
         <v>500</v>
       </c>
-      <c r="F34" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="G34" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
+      <c r="F34" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="G34" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
     </row>
     <row r="35" ht="28.5">
-      <c r="A35" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="C35" s="14" t="s">
+      <c r="A35" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="D35" s="14" t="s">
+      <c r="B35" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="E35" s="16">
+      <c r="C35" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E35" s="17">
         <v>1.5</v>
       </c>
-      <c r="F35" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="G35" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
+      <c r="F35" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="G35" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
     </row>
     <row r="36" ht="14.25">
-      <c r="A36" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="C36" s="14" t="s">
+      <c r="A36" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D36" s="14" t="s">
+      <c r="B36" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E36" s="16">
+      <c r="C36" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="E36" s="17">
         <v>2.5</v>
       </c>
-      <c r="F36" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="G36" s="14" t="s">
-        <v>169</v>
-      </c>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
+      <c r="F36" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
     </row>
     <row r="37" ht="28.5">
-      <c r="A37" s="14" t="s">
-        <v>170</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>171</v>
-      </c>
-      <c r="C37" s="14" t="s">
+      <c r="A37" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="D37" s="14" t="s">
+      <c r="B37" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="E37" s="14">
+      <c r="C37" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="E37" s="15">
         <v>500</v>
       </c>
-      <c r="F37" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="G37" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
+      <c r="F37" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="H37" s="15"/>
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
     </row>
     <row r="38" ht="28.5">
-      <c r="A38" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="C38" s="14" t="s">
+      <c r="A38" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="D38" s="14" t="s">
+      <c r="B38" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="E38" s="14">
+      <c r="C38" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="E38" s="15">
         <v>100</v>
       </c>
-      <c r="F38" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="G38" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="H38" s="14"/>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
+      <c r="F38" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="G38" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H38" s="15"/>
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
     </row>
     <row r="39" ht="28.5">
-      <c r="A39" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C39" s="14" t="s">
+      <c r="A39" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="D39" s="14" t="s">
+      <c r="B39" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="E39" s="17">
+      <c r="C39" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="18">
         <v>67000000</v>
       </c>
-      <c r="F39" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="G39" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="H39" s="14"/>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
+      <c r="F39" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="G39" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="H39" s="15"/>
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
     </row>
     <row r="40" ht="14.25">
       <c r="A40" s="1"/>
